--- a/task183/golden/cable_program_2027.xlsx
+++ b/task183/golden/cable_program_2027.xlsx
@@ -192,7 +192,7 @@
     <t>4. Sustained interruption: more than five minutes for the customer, timed to that customer's own restoration step (TVE-RS-04 3.3); customers served from the connectivity model on 30 September 2026 (3.2).</t>
   </si>
   <si>
-    <t>5. Major event days RY2026 (2.5 beta, threshold 13.60 min of daily SAIDI from RY2021 to RY2025): 25 Jan 2026, 28 Jul 2026. Left out of SAIFI and SAIDI, kept in the 4+ count (TVE-RS-04 6.1).</t>
+    <t>5. Major event days RY2026 (2.5 beta, threshold 13.72 min of daily SAIDI from RY2021 to RY2025): 25 Jan 2026, 28 Jul 2026. Left out of SAIFI and SAIDI, kept in the 4+ count (TVE-RS-04 6.1).</t>
   </si>
   <si>
     <t>6. Substation bank outages counted once per customer on each feeder, not at the outage totals the OMS export repeats on each feeder row.</t>
@@ -1069,7 +1069,7 @@
         <v>45</v>
       </c>
       <c r="B2" s="23">
-        <v>37510.7</v>
+        <v>37507.1</v>
       </c>
       <c r="C2" s="24">
         <v>841</v>
@@ -1083,13 +1083,13 @@
         <v>46</v>
       </c>
       <c r="B3" s="23">
-        <v>2726.7</v>
+        <v>2730.2</v>
       </c>
       <c r="C3" s="24">
         <v>55</v>
       </c>
       <c r="D3" s="25">
-        <v>0.0202</v>
+        <v>0.0201</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
